--- a/Excel/测试登录参数化.xlsx
+++ b/Excel/测试登录参数化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" activeTab="1"/>
+    <workbookView windowWidth="21600" windowHeight="9105"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>场景</t>
   </si>
@@ -1232,8 +1232,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="27.1592920353982" style="1" customWidth="1"/>
     <col min="2" max="2" width="48.6637168141593" style="1" customWidth="1"/>
@@ -1286,6 +1286,14 @@
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/测试登录参数化.xlsx
+++ b/Excel/测试登录参数化.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>场景</t>
   </si>
@@ -64,12 +63,6 @@
   </si>
   <si>
     <t>顾客编号不能为空</t>
-  </si>
-  <si>
-    <t>acc</t>
-  </si>
-  <si>
-    <t>登录成功</t>
   </si>
 </sst>
 </file>
@@ -1300,36 +1293,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
-  <cols>
-    <col min="1" max="2" width="14.6106194690265" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.02654867256637" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1">
-        <v>60003156</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/Excel/测试登录参数化.xlsx
+++ b/Excel/测试登录参数化.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>场景</t>
   </si>
@@ -693,8 +696,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -1225,68 +1231,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="27.1592920353982" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.6637168141593" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.02654867256637" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="27.1592920353982" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.6637168141593" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9.02654867256637" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
